--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486289_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486289_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7149</v>
+        <v>5.4721</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1729</v>
+        <v>4.8376</v>
       </c>
       <c r="F2" t="n">
-        <v>0.542</v>
+        <v>0.6345</v>
       </c>
       <c r="G2" t="n">
         <v>3.7021</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9677</v>
+        <v>0.7249</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8292</v>
+        <v>0.4939</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1385</v>
+        <v>0.231</v>
       </c>
       <c r="V2" t="n">
         <v>-1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7727</v>
+        <v>4.1071</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5211</v>
+        <v>5.7014</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7484</v>
+        <v>-1.5943</v>
       </c>
       <c r="G3" t="n">
         <v>1.1311</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4008</v>
+        <v>-0.0664</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1334</v>
+        <v>0.0469</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2674</v>
+        <v>-0.1133</v>
       </c>
       <c r="V3" t="n">
         <v>2.8249</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.752</v>
+        <v>3.1935</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7819</v>
+        <v>3.2542</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0299</v>
+        <v>-0.0607</v>
       </c>
       <c r="G4" t="n">
         <v>1.8841</v>
@@ -766,13 +766,13 @@
         <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.2557</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2812</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0564</v>
+        <v>0.0255</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1735</v>
+        <v>1.4462</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8473</v>
+        <v>4.0276</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6738</v>
+        <v>-2.5813</v>
       </c>
       <c r="G5" t="n">
         <v>1.4244</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6817</v>
+        <v>0.9545</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3581</v>
+        <v>0.5384</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3236</v>
+        <v>0.4161</v>
       </c>
       <c r="V5" t="n">
         <v>-2.4552</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0635</v>
+        <v>0.0044</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8719</v>
+        <v>0.569</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8084</v>
+        <v>-0.5646</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1436</v>
+        <v>-0.4667</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2257</v>
+        <v>1.4904</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-1.9571</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6028</v>
+        <v>1.4132</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4115</v>
+        <v>2.1383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1912</v>
+        <v>-0.7251</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4592</v>
+        <v>-1.8799</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1858</v>
+        <v>-0.6479</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2733</v>
+        <v>-1.232</v>
       </c>
       <c r="P6" t="n">
         <v>-0.2175</v>
@@ -922,28 +922,28 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4419</v>
+        <v>0.4933</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5312</v>
+        <v>0.0481</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0893</v>
+        <v>0.4452</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3045</v>
+        <v>0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1745</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1453</v>
+        <v>-0.0888</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5097</v>
+        <v>0.1131</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3644</v>
+        <v>-0.2019</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0287</v>
+        <v>-1.2924</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.216</v>
+        <v>-1.5482</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1873</v>
+        <v>0.2558</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0382</v>
+        <v>-0.7687</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-1.3624</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>0.5937</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.067</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.216</v>
+        <v>-0.1858</v>
       </c>
       <c r="O7" t="n">
-        <v>0.149</v>
+        <v>-0.3379</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6012</v>
+        <v>-0.5789</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5396</v>
+        <v>-0.4434</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0616</v>
+        <v>-0.1355</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3262</v>
+        <v>-0.3196</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0535</v>
+        <v>-0.7765</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3797</v>
+        <v>0.4569</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4667</v>
+        <v>-0.0287</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4904</v>
+        <v>-0.216</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9571</v>
+        <v>0.1873</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4132</v>
+        <v>0.0382</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1383</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7251</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8799</v>
+        <v>-0.067</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6479</v>
+        <v>-0.216</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.232</v>
+        <v>0.149</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1627</v>
+        <v>0.4269</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4675</v>
+        <v>0.2728</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6302</v>
+        <v>0.1541</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0.3698</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4502</v>
+        <v>-0.5193</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4024</v>
+        <v>0.3816</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0478</v>
+        <v>-0.9009</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2924</v>
+        <v>1.1436</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5482</v>
+        <v>1.2257</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2558</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7687</v>
+        <v>1.6028</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3624</v>
+        <v>1.4115</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5937</v>
+        <v>0.1912</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.4592</v>
       </c>
       <c r="N9" t="n">
         <v>-0.1858</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3379</v>
+        <v>-0.2733</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9403</v>
+        <v>-0.1409</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9589</v>
+        <v>0.0409</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0186</v>
+        <v>-0.1818</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>-1.3045</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3252</v>
+        <v>-0.1745</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2592</v>
+        <v>-2.0665</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0179</v>
+        <v>-1.7944</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2413</v>
+        <v>-0.2721</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9577</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4385</v>
+        <v>0.6312</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1526</v>
+        <v>0.3761</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2859</v>
+        <v>0.2551</v>
       </c>
       <c r="V10" t="n">
         <v>1.695</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4916</v>
+        <v>-2.609</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6545</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1462</v>
+        <v>-3.177</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2999</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0035</v>
+        <v>-0.1139</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0601</v>
+        <v>-0.0264</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0566</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7065</v>
+        <v>-2.8375</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6968</v>
+        <v>-1.9203</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0097</v>
+        <v>-0.9172</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0527</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6937</v>
+        <v>0.5627</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5636</v>
+        <v>0.3401</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1301</v>
+        <v>0.2226</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0976</v>
+        <v>5.7826</v>
       </c>
       <c r="E13" t="n">
-        <v>14.2763</v>
+        <v>14.9613</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.178800000000001</v>
+        <v>-9.178599999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8128</v>
@@ -1468,10 +1468,10 @@
         <v>10.8752</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9527</v>
+        <v>2.6377</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7211</v>
+        <v>1.4062</v>
       </c>
       <c r="U13" t="n">
         <v>1.2316</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8917</v>
+        <v>2.9496</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5753</v>
+        <v>2.9105</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3165</v>
+        <v>0.0391</v>
       </c>
       <c r="G14" t="n">
         <v>2.9175</v>
@@ -1546,13 +1546,13 @@
         <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2571</v>
+        <v>-0.1992</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3594</v>
+        <v>0.082</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4212</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4223</v>
+        <v>2.1886</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1475</v>
+        <v>2.924</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7252</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.2412</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2656</v>
+        <v>-0.4993</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3509</v>
+        <v>-0.5744</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0853</v>
+        <v>0.0751</v>
       </c>
       <c r="V15" t="n">
         <v>1.6642</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6245</v>
+        <v>1.6861</v>
       </c>
       <c r="E16" t="n">
         <v>1.5968</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0277</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>1.0403</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4881</v>
+        <v>0.5498</v>
       </c>
       <c r="T16" t="n">
         <v>0.3341</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1541</v>
+        <v>0.2157</v>
       </c>
       <c r="V16" t="n">
         <v>-0.339</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5015</v>
+        <v>1.1902</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2733</v>
+        <v>2.2622</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7718</v>
+        <v>-1.0721</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1263</v>
+        <v>1.0737</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6051</v>
+        <v>0.1214</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5212</v>
+        <v>0.9522</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7549</v>
+        <v>2.7792</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8696</v>
+        <v>1.1711</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1147</v>
+        <v>1.6081</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3714</v>
+        <v>-1.7056</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2645</v>
+        <v>-1.0497</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6359</v>
+        <v>-0.6558</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2713</v>
+        <v>-0.7652</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6377</v>
+        <v>-0.5371</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6335</v>
+        <v>-0.228</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0785</v>
+        <v>1.0992</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3904</v>
+        <v>1.3252</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.469</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3642</v>
+        <v>0.5994</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7034</v>
+        <v>2.4225</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3392</v>
+        <v>-1.8231</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0737</v>
+        <v>3.7609</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1214</v>
+        <v>2.4484</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9522</v>
+        <v>1.3124</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7792</v>
+        <v>4.9986</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1711</v>
+        <v>3.5618</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6081</v>
+        <v>1.4368</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7056</v>
+        <v>-1.2377</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0497</v>
+        <v>-1.1134</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6558</v>
+        <v>-0.1243</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5912</v>
+        <v>-0.4299</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0959</v>
+        <v>-0.4434</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4952</v>
+        <v>0.0135</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0992</v>
+        <v>-0.339</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.226</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>S. LLORENTE PAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0599</v>
+        <v>0.2386</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9755</v>
+        <v>0.0545</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9156</v>
+        <v>0.184</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7609</v>
+        <v>0.301</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4484</v>
+        <v>0.152</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3124</v>
+        <v>0.149</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9986</v>
+        <v>0.0365</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5618</v>
+        <v>0.0365</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4368</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2377</v>
+        <v>0.2645</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1134</v>
+        <v>0.1155</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1243</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9694</v>
+        <v>-0.0625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8904</v>
+        <v>0.018</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.079</v>
+        <v>-0.0805</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.339</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LLORENTE PAZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.015</v>
+        <v>-0.4214</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.169</v>
+        <v>0.5969</v>
       </c>
       <c r="F20" t="n">
-        <v>0.184</v>
+        <v>-1.0184</v>
       </c>
       <c r="G20" t="n">
-        <v>0.301</v>
+        <v>-1.1263</v>
       </c>
       <c r="H20" t="n">
-        <v>0.152</v>
+        <v>-0.6051</v>
       </c>
       <c r="I20" t="n">
-        <v>0.149</v>
+        <v>-0.5212</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0365</v>
+        <v>-0.7549</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0365</v>
+        <v>-0.8696</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
+        <v>-0.3714</v>
+      </c>
+      <c r="N20" t="n">
         <v>0.2645</v>
       </c>
-      <c r="N20" t="n">
-        <v>0.1155</v>
-      </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>-0.6359</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.286</v>
+        <v>1.3483</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2055</v>
+        <v>0.9614</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0805</v>
+        <v>0.3869</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0785</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4849</v>
+        <v>-0.6918</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1831</v>
+        <v>0.4008</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.668</v>
+        <v>-1.0926</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6936</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.065</v>
+        <v>-0.2719</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5997</v>
+        <v>-0.1826</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6647</v>
+        <v>-0.0892</v>
       </c>
       <c r="V21" t="n">
         <v>2.4037</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0601</v>
+        <v>-1.509</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6863</v>
+        <v>-0.351</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3738</v>
+        <v>-1.158</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5327</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2107</v>
+        <v>0.3404</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2055</v>
+        <v>0.1298</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0052</v>
+        <v>0.2106</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5342</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4255</v>
+        <v>-2.8846</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6548</v>
+        <v>-0.3196</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7706</v>
+        <v>-2.5651</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7554999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8307</v>
+        <v>-0.2899</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>-0.4867</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1968</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5342</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.0063</v>
+        <v>-6.953</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7661</v>
+        <v>-3.319</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2402</v>
+        <v>-3.634</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4138</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2365</v>
+        <v>-0.1833</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6201</v>
+        <v>-0.0138</v>
       </c>
       <c r="V24" t="n">
         <v>-3.6159</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.097699999999998</v>
+        <v>-3.6073</v>
       </c>
       <c r="E25" t="n">
-        <v>9.178700000000001</v>
+        <v>9.178599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.2762</v>
+        <v>-12.7862</v>
       </c>
       <c r="G25" t="n">
-        <v>1.812699999999999</v>
+        <v>1.812699999999998</v>
       </c>
       <c r="H25" t="n">
         <v>2.235</v>
@@ -2389,7 +2389,7 @@
         <v>-10.2174</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.758500000000001</v>
+        <v>-3.7585</v>
       </c>
       <c r="O25" t="n">
         <v>-6.4587</v>
@@ -2404,13 +2404,13 @@
         <v>7.612499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.952799999999999</v>
+        <v>-0.4627</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2317</v>
+        <v>-1.2315</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7212</v>
+        <v>0.7691</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6949</v>
